--- a/product_selector_out/STM32L1 series.xlsx
+++ b/product_selector_out/STM32L1 series.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -69,6 +69,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -85,7 +90,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -99,6 +104,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8175,7 +8181,7 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9489,7 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10464,7 +10470,7 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10797,7 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12426,7 +12432,7 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15696,7 +15702,7 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20274,7 +20280,7 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20928,7 +20934,7 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24198,7 +24204,7 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25506,7 +25512,7 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -26814,7 +26820,7 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -29350,7 +29356,7 @@
       </c>
       <c r="AW98" s="4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="AX98" s="4" t="inlineStr">
@@ -30339,9 +30345,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW12" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW12" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX12" s="7" t="inlineStr">
@@ -30666,9 +30672,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX13" s="7" t="inlineStr">
@@ -30993,9 +30999,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX14" s="7" t="inlineStr">
@@ -31320,9 +31326,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX15" s="7" t="inlineStr">
@@ -31647,9 +31653,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX16" s="7" t="inlineStr">
@@ -31974,9 +31980,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW17" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW17" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX17" s="7" t="inlineStr">
@@ -32301,9 +32307,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX18" s="7" t="inlineStr">
@@ -32628,9 +32634,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX19" s="7" t="inlineStr">
@@ -32955,9 +32961,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX20" s="7" t="inlineStr">
@@ -33282,9 +33288,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX21" s="7" t="inlineStr">
@@ -33609,9 +33615,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX22" s="7" t="inlineStr">
@@ -33936,9 +33942,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX23" s="7" t="inlineStr">
@@ -34263,9 +34269,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX24" s="7" t="inlineStr">
@@ -34590,9 +34596,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX25" s="7" t="inlineStr">
@@ -34917,9 +34923,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX26" s="7" t="inlineStr">
@@ -35244,9 +35250,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW27" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW27" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX27" s="7" t="inlineStr">
@@ -35571,9 +35577,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX28" s="7" t="inlineStr">
@@ -35898,9 +35904,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW29" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW29" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX29" s="7" t="inlineStr">
@@ -36225,9 +36231,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX30" s="7" t="inlineStr">
@@ -36552,9 +36558,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX31" s="7" t="inlineStr">
@@ -36879,9 +36885,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW32" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW32" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX32" s="7" t="inlineStr">
@@ -36986,9 +36992,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -37206,14 +37212,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY33" s="6" t="inlineStr">
@@ -37286,9 +37292,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -37533,9 +37539,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW34" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW34" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX34" s="7" t="inlineStr">
@@ -37860,9 +37866,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW35" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW35" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX35" s="7" t="inlineStr">
@@ -38187,9 +38193,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW36" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW36" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX36" s="7" t="inlineStr">
@@ -38294,9 +38300,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -38514,14 +38520,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY37" s="6" t="inlineStr">
@@ -38594,9 +38600,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38841,9 +38847,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW38" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW38" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX38" s="7" t="inlineStr">
@@ -39168,9 +39174,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW39" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX39" s="7" t="inlineStr">
@@ -39275,9 +39281,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -39495,14 +39501,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY40" s="6" t="inlineStr">
@@ -39575,9 +39581,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -39602,9 +39608,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -39822,14 +39828,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY41" s="6" t="inlineStr">
@@ -39902,9 +39908,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40149,9 +40155,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW42" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW42" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX42" s="7" t="inlineStr">
@@ -40476,9 +40482,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW43" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX43" s="7" t="inlineStr">
@@ -40803,9 +40809,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW44" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW44" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX44" s="7" t="inlineStr">
@@ -41130,9 +41136,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW45" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW45" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX45" s="7" t="inlineStr">
@@ -41237,9 +41243,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -41457,14 +41463,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY46" s="6" t="inlineStr">
@@ -41537,9 +41543,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41784,9 +41790,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW47" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW47" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX47" s="7" t="inlineStr">
@@ -42111,9 +42117,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW48" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW48" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX48" s="7" t="inlineStr">
@@ -42438,9 +42444,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW49" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW49" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX49" s="7" t="inlineStr">
@@ -42765,9 +42771,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW50" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW50" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX50" s="7" t="inlineStr">
@@ -43092,9 +43098,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW51" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW51" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX51" s="7" t="inlineStr">
@@ -43419,9 +43425,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW52" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW52" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX52" s="7" t="inlineStr">
@@ -43746,9 +43752,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW53" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW53" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX53" s="7" t="inlineStr">
@@ -44073,9 +44079,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW54" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX54" s="7" t="inlineStr">
@@ -44400,9 +44406,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW55" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW55" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX55" s="7" t="inlineStr">
@@ -44507,9 +44513,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -44727,14 +44733,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY56" s="6" t="inlineStr">
@@ -44807,9 +44813,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -45054,9 +45060,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW57" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW57" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX57" s="7" t="inlineStr">
@@ -45381,9 +45387,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW58" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW58" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX58" s="7" t="inlineStr">
@@ -45708,9 +45714,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW59" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW59" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX59" s="7" t="inlineStr">
@@ -46035,9 +46041,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW60" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW60" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX60" s="7" t="inlineStr">
@@ -46362,9 +46368,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW61" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW61" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX61" s="7" t="inlineStr">
@@ -46689,9 +46695,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW62" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW62" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX62" s="7" t="inlineStr">
@@ -47016,9 +47022,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW63" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW63" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX63" s="7" t="inlineStr">
@@ -47343,9 +47349,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW64" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW64" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX64" s="7" t="inlineStr">
@@ -47670,9 +47676,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW65" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW65" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX65" s="7" t="inlineStr">
@@ -47997,9 +48003,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW66" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW66" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX66" s="7" t="inlineStr">
@@ -48324,9 +48330,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW67" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW67" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX67" s="7" t="inlineStr">
@@ -48651,9 +48657,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW68" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW68" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX68" s="7" t="inlineStr">
@@ -48978,9 +48984,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW69" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW69" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX69" s="7" t="inlineStr">
@@ -49085,9 +49091,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -49305,14 +49311,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY70" s="6" t="inlineStr">
@@ -49385,9 +49391,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49632,9 +49638,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW71" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW71" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX71" s="7" t="inlineStr">
@@ -49739,9 +49745,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -49959,14 +49965,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY72" s="6" t="inlineStr">
@@ -50039,9 +50045,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -50286,9 +50292,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW73" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW73" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX73" s="7" t="inlineStr">
@@ -50613,9 +50619,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW74" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW74" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX74" s="7" t="inlineStr">
@@ -50940,9 +50946,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW75" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW75" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX75" s="7" t="inlineStr">
@@ -51267,9 +51273,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW76" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW76" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX76" s="7" t="inlineStr">
@@ -51594,9 +51600,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW77" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW77" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX77" s="7" t="inlineStr">
@@ -51921,9 +51927,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW78" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW78" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX78" s="7" t="inlineStr">
@@ -52248,9 +52254,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW79" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW79" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX79" s="7" t="inlineStr">
@@ -52575,9 +52581,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW80" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW80" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX80" s="7" t="inlineStr">
@@ -52902,9 +52908,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW81" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW81" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX81" s="7" t="inlineStr">
@@ -53009,9 +53015,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -53229,14 +53235,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY82" s="6" t="inlineStr">
@@ -53309,9 +53315,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53556,9 +53562,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW83" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW83" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX83" s="7" t="inlineStr">
@@ -53883,9 +53889,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW84" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX84" s="7" t="inlineStr">
@@ -54210,9 +54216,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW85" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW85" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX85" s="7" t="inlineStr">
@@ -54317,9 +54323,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -54537,14 +54543,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY86" s="6" t="inlineStr">
@@ -54617,9 +54623,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54864,9 +54870,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW87" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW87" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX87" s="7" t="inlineStr">
@@ -55191,9 +55197,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW88" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW88" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX88" s="7" t="inlineStr">
@@ -55518,9 +55524,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW89" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW89" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX89" s="7" t="inlineStr">
@@ -55625,9 +55631,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -55845,14 +55851,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AX90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY90" s="6" t="inlineStr">
@@ -55925,9 +55931,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -56172,9 +56178,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW91" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW91" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX91" s="7" t="inlineStr">
@@ -56499,9 +56505,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW92" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW92" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX92" s="7" t="inlineStr">
@@ -56826,9 +56832,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW93" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW93" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX93" s="7" t="inlineStr">
@@ -57153,9 +57159,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW94" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW94" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX94" s="7" t="inlineStr">
@@ -57480,9 +57486,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW95" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW95" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX95" s="7" t="inlineStr">
@@ -57807,9 +57813,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW96" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW96" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX96" s="7" t="inlineStr">
@@ -58134,9 +58140,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW97" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW97" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX97" s="7" t="inlineStr">
@@ -58461,9 +58467,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW98" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW98" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
         </is>
       </c>
       <c r="AX98" s="7" t="inlineStr">
@@ -58562,7 +58568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -58593,7 +58599,1678 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>STM32L162QD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>STM32L162ZD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>STM32L162QC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32L162VC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32L162RC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32L162RD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32L162VD-X</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32L162VE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32L162RC-A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>STM32L162VD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32L162ZE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32L162ZC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32L162RE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32L162VC-A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32L151CB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32L151VD-X</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32L152CB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32L151C8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32L152C8</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32L152QE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32L152RE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32L151VE</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32L151ZE</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32L151C6-A</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32L152UC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STM32L151R8-A</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STM32L151QE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STM32L151R6-A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STM32L151RE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STM32L152ZE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>STM32L151C8-A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>STM32L152VC</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>STM32L152QC</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>STM32L151QC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>STM32L152ZC</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>STM32L151ZC</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>STM32L151CC</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>STM32L151RB-A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>STM32L151R6</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>STM32L152CC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>STM32L151RC</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>STM32L151VC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>STM32L152RC</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>STM32L152QD</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>STM32L151QD</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>STM32L152R8</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>STM32L151ZD</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>STM32L152ZD</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>STM32L152RD</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>STM32L151RD</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>STM32L152C6</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>STM32L152VD</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>STM32L151VD</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>STM32L152R6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>STM32L151C6</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>STM32L151VB</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>STM32L152VB</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>STM32L151V8</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>STM32L152V8</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>STM32L151RB</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>STM32L152RB</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>STM32L151V8-A</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>STM32L151VB-A</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>STM32L151RC-A</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>STM32L151CB-A</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>STM32L151UC</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>STM32L151R8</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>STM32L152VE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>STM32L151VC-A</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>STM32L100C6-A</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>STM32L100C6</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>STM32L100RB-A</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>STM32L100R8</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>STM32L100RB</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>STM32L100R8-A</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>STM32L100RC</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/product_selector_out/STM32L1 series.xlsx
+++ b/product_selector_out/STM32L1 series.xlsx
@@ -8181,7 +8181,7 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -10797,7 +10797,7 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -20280,7 +20280,7 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
         </is>
       </c>
     </row>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
     </row>
@@ -36992,9 +36992,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -37212,14 +37212,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW33" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY33" s="6" t="inlineStr">
@@ -37292,9 +37292,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -38300,9 +38300,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -38520,14 +38520,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW37" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY37" s="6" t="inlineStr">
@@ -38600,9 +38600,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -39281,9 +39281,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -39501,14 +39501,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW40" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY40" s="6" t="inlineStr">
@@ -39581,9 +39581,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -39608,9 +39608,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -39828,14 +39828,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW41" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY41" s="6" t="inlineStr">
@@ -39908,9 +39908,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -41243,9 +41243,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -41463,14 +41463,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW46" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX46" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY46" s="6" t="inlineStr">
@@ -41543,9 +41543,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -44513,9 +44513,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -44733,14 +44733,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW56" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX56" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY56" s="6" t="inlineStr">
@@ -44813,9 +44813,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -49091,9 +49091,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -49311,14 +49311,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW70" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX70" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY70" s="6" t="inlineStr">
@@ -49391,9 +49391,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -49745,9 +49745,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -49965,14 +49965,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW72" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX72" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY72" s="6" t="inlineStr">
@@ -50045,9 +50045,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -53015,9 +53015,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -53235,14 +53235,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW82" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX82" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY82" s="6" t="inlineStr">
@@ -53315,9 +53315,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -54323,9 +54323,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -54543,14 +54543,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW86" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX86" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY86" s="6" t="inlineStr">
@@ -54623,9 +54623,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -55631,9 +55631,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -55851,14 +55851,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AX90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AW90" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AX90" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AY90" s="6" t="inlineStr">
@@ -55931,9 +55931,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BM90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -58568,7 +58568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -59064,7 +59064,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L151VE</t>
+          <t>STM32L152C6-A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -59079,14 +59079,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L151ZE</t>
+          <t>STM32L151VE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -59108,7 +59108,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L151C6-A</t>
+          <t>STM32L151ZE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -59130,7 +59130,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L152UC</t>
+          <t>STM32L151C6-A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -59145,14 +59145,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L151R8-A</t>
+          <t>STM32L152VC-A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -59174,7 +59174,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L151QE</t>
+          <t>STM32L152UC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -59189,14 +59189,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L151R6-A</t>
+          <t>STM32L151R8-A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -59218,7 +59218,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L151RE</t>
+          <t>STM32L152VD-X</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -59233,14 +59233,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L152ZE</t>
+          <t>STM32L152R6-A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -59255,14 +59255,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L151C8-A</t>
+          <t>STM32L151QE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -59284,7 +59284,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L152VC</t>
+          <t>STM32L151R6-A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -59299,14 +59299,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L152QC</t>
+          <t>STM32L151RE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -59328,7 +59328,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L151QC</t>
+          <t>STM32L152ZE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -59350,7 +59350,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L152ZC</t>
+          <t>STM32L152C8-A</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -59365,14 +59365,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L151ZC</t>
+          <t>STM32L151C8-A</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -59394,7 +59394,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L151CC</t>
+          <t>STM32L152VC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -59416,7 +59416,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L151RB-A</t>
+          <t>STM32L152QC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -59438,7 +59438,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L151R6</t>
+          <t>STM32L151QC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -59460,7 +59460,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L152CC</t>
+          <t>STM32L152ZC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -59475,14 +59475,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L151RC</t>
+          <t>STM32L151ZC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -59497,14 +59497,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L151VC</t>
+          <t>STM32L151CC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -59526,7 +59526,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L152RC</t>
+          <t>STM32L151RB-A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -59541,14 +59541,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L152QD</t>
+          <t>STM32L151R6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -59570,7 +59570,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L151QD</t>
+          <t>STM32L152R8-A</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -59585,14 +59585,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L152R8</t>
+          <t>STM32L152CC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -59607,14 +59607,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L151ZD</t>
+          <t>STM32L151RC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -59629,14 +59629,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L152ZD</t>
+          <t>STM32L151VC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -59651,14 +59651,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L152RD</t>
+          <t>STM32L152RC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -59673,14 +59673,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L151RD</t>
+          <t>STM32L152QD</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -59702,7 +59702,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L152C6</t>
+          <t>STM32L151QD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -59724,7 +59724,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L152VD</t>
+          <t>STM32L152R8</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -59746,7 +59746,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L151VD</t>
+          <t>STM32L151ZD</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -59768,7 +59768,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L152R6</t>
+          <t>STM32L152ZD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -59790,7 +59790,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L151C6</t>
+          <t>STM32L152RD</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -59812,7 +59812,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L151VB</t>
+          <t>STM32L151RD</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -59834,7 +59834,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L152VB</t>
+          <t>STM32L152C6</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -59856,7 +59856,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L151V8</t>
+          <t>STM32L152VD</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -59878,7 +59878,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L152V8</t>
+          <t>STM32L152CB-A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -59893,14 +59893,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L151RB</t>
+          <t>STM32L151VD</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -59922,7 +59922,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L152RB</t>
+          <t>STM32L152V8-A</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -59937,14 +59937,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L151V8-A</t>
+          <t>STM32L152R6</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -59966,7 +59966,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L151VB-A</t>
+          <t>STM32L151C6</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -59988,7 +59988,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L151RC-A</t>
+          <t>STM32L151VB</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -60010,7 +60010,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L151CB-A</t>
+          <t>STM32L152VB</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -60032,7 +60032,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L151UC</t>
+          <t>STM32L151V8</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -60047,14 +60047,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L151R8</t>
+          <t>STM32L152V8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -60076,7 +60076,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L152VE</t>
+          <t>STM32L151RB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -60098,7 +60098,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L151VC-A</t>
+          <t>STM32L152RB</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -60120,7 +60120,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L100C6-A</t>
+          <t>STM32L151V8-A</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -60135,14 +60135,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32L100C6</t>
+          <t>STM32L152VB-A</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -60157,14 +60157,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32L100RB-A</t>
+          <t>STM32L151VB-A</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -60179,14 +60179,14 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32L100R8</t>
+          <t>STM32L151RC-A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -60201,14 +60201,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32L100RB</t>
+          <t>STM32L151CB-A</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -60223,14 +60223,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32L100R8-A</t>
+          <t>STM32L152RB-A</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -60245,27 +60245,269 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>STM32L151UC</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>STM32L151R8</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>STM32L152VE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>STM32L152RC-A</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>STM32L151VC-A</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>STM32L100C6-A</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>STM32L100C6</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>STM32L100RB-A</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>STM32L100R8</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>STM32L100RB</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>STM32L100R8-A</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>STM32L100RC</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>

--- a/product_selector_out/STM32L1 series.xlsx
+++ b/product_selector_out/STM32L1 series.xlsx
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l162qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l162qc.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l162rc.pdf</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l162qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -9489,7 +9489,7 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10797,7 +10797,7 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12432,7 +12432,7 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -15702,7 +15702,7 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20280,7 +20280,7 @@
       </c>
       <c r="BM70" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -20934,7 +20934,7 @@
       </c>
       <c r="BM72" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -24204,7 +24204,7 @@
       </c>
       <c r="BM82" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -24858,7 +24858,7 @@
       </c>
       <c r="BM84" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -25512,7 +25512,7 @@
       </c>
       <c r="BM86" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6-a.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="BM90" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -27147,7 +27147,7 @@
       </c>
       <c r="BM91" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
     </row>
@@ -28128,7 +28128,7 @@
       </c>
       <c r="BM94" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
     </row>
@@ -29109,7 +29109,7 @@
       </c>
       <c r="BM97" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
     </row>
@@ -32087,9 +32087,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -32307,14 +32307,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -32387,9 +32387,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -34376,9 +34376,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -34596,14 +34596,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW25" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -34676,9 +34676,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -36992,9 +36992,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
@@ -37212,14 +37212,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW33" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX33" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY33" s="6" t="inlineStr">
@@ -37292,9 +37292,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38300,9 +38300,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
@@ -38520,14 +38520,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW37" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX37" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX37" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY37" s="6" t="inlineStr">
@@ -38600,9 +38600,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -38954,9 +38954,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
@@ -39174,14 +39174,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW39" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX39" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY39" s="6" t="inlineStr">
@@ -39254,9 +39254,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -39281,9 +39281,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
@@ -39501,14 +39501,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW40" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX40" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX40" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY40" s="6" t="inlineStr">
@@ -39581,9 +39581,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -39608,9 +39608,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -39828,14 +39828,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW41" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX41" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX41" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY41" s="6" t="inlineStr">
@@ -39908,9 +39908,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -40262,9 +40262,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
@@ -40482,14 +40482,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW43" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX43" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX43" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY43" s="6" t="inlineStr">
@@ -40562,9 +40562,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -41243,9 +41243,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -41463,14 +41463,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW46" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX46" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX46" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY46" s="6" t="inlineStr">
@@ -41543,9 +41543,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -43859,9 +43859,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -44079,14 +44079,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW54" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX54" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX54" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY54" s="6" t="inlineStr">
@@ -44159,9 +44159,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -44513,9 +44513,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -44733,14 +44733,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW56" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX56" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX56" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY56" s="6" t="inlineStr">
@@ -44813,9 +44813,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49091,9 +49091,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -49311,14 +49311,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW70" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX70" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX70" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY70" s="6" t="inlineStr">
@@ -49391,9 +49391,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM70" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -49745,9 +49745,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -49965,14 +49965,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW72" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX72" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX72" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY72" s="6" t="inlineStr">
@@ -50045,9 +50045,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM72" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53015,9 +53015,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -53235,14 +53235,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW82" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX82" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX82" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY82" s="6" t="inlineStr">
@@ -53315,9 +53315,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM82" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -53669,9 +53669,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -53889,14 +53889,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW84" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX84" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX84" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY84" s="6" t="inlineStr">
@@ -53969,9 +53969,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM84" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -54323,9 +54323,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
@@ -54543,14 +54543,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW86" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX86" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX86" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY86" s="6" t="inlineStr">
@@ -54623,9 +54623,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM86" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -55631,9 +55631,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
@@ -55851,14 +55851,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW90" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX90" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX90" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY90" s="6" t="inlineStr">
@@ -55931,9 +55931,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM90" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BM90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -58568,7 +58568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -58734,7 +58734,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32L162VD-X</t>
+          <t>STM32L162VE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -58756,7 +58756,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32L162VE</t>
+          <t>STM32L162RC-A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -58771,14 +58771,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32L162RC-A</t>
+          <t>STM32L162VD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -58793,14 +58793,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32L162VD</t>
+          <t>STM32L162ZE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -58815,14 +58815,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32L162ZE</t>
+          <t>STM32L162ZC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -58844,7 +58844,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32L162ZC</t>
+          <t>STM32L162RE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -58866,7 +58866,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32L162RE</t>
+          <t>STM32L151CB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -58888,7 +58888,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32L162VC-A</t>
+          <t>STM32L151VD-X</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -58903,14 +58903,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32L151CB</t>
+          <t>STM32L152CB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -58932,7 +58932,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32L151VD-X</t>
+          <t>STM32L151C8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -58954,7 +58954,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32L152CB</t>
+          <t>STM32L152C8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -58976,7 +58976,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32L151C8</t>
+          <t>STM32L152QE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -58998,7 +58998,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32L152C8</t>
+          <t>STM32L152RE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -59020,7 +59020,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32L152QE</t>
+          <t>STM32L151VE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -59042,7 +59042,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32L152RE</t>
+          <t>STM32L151ZE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -59064,7 +59064,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32L152C6-A</t>
+          <t>STM32L151C6-A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -59079,14 +59079,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32L151VE</t>
+          <t>STM32L152UC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -59101,14 +59101,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32L151ZE</t>
+          <t>STM32L151QE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -59130,7 +59130,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32L151C6-A</t>
+          <t>STM32L151RE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -59152,7 +59152,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32L152VC-A</t>
+          <t>STM32L152ZE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -59174,7 +59174,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32L152UC</t>
+          <t>STM32L151C8-A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -59189,14 +59189,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32L151R8-A</t>
+          <t>STM32L152VC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -59211,14 +59211,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32L152VD-X</t>
+          <t>STM32L152QC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -59233,14 +59233,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32L152R6-A</t>
+          <t>STM32L151QC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -59255,14 +59255,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32L151QE</t>
+          <t>STM32L152ZC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -59284,7 +59284,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32L151R6-A</t>
+          <t>STM32L151ZC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -59306,7 +59306,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32L151RE</t>
+          <t>STM32L151CC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -59321,14 +59321,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32L152ZE</t>
+          <t>STM32L151R6</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -59350,7 +59350,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32L152C8-A</t>
+          <t>STM32L152CC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -59372,7 +59372,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32L151C8-A</t>
+          <t>STM32L151RC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -59387,14 +59387,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32L152VC</t>
+          <t>STM32L151VC</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -59416,7 +59416,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32L152QC</t>
+          <t>STM32L152RC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -59431,14 +59431,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32L151QC</t>
+          <t>STM32L152QD</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -59460,7 +59460,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32L152ZC</t>
+          <t>STM32L151QD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -59482,7 +59482,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32L151ZC</t>
+          <t>STM32L152R8</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -59504,7 +59504,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32L151CC</t>
+          <t>STM32L151ZD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -59519,14 +59519,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32L151RB-A</t>
+          <t>STM32L152ZD</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -59548,7 +59548,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32L151R6</t>
+          <t>STM32L152RD</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -59570,7 +59570,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32L152R8-A</t>
+          <t>STM32L151RD</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -59585,14 +59585,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32L152CC</t>
+          <t>STM32L152C6</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -59607,14 +59607,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32L151RC</t>
+          <t>STM32L152VD</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -59629,14 +59629,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32L151VC</t>
+          <t>STM32L151VD</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -59651,14 +59651,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32L152RC</t>
+          <t>STM32L152R6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -59673,14 +59673,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32L152QD</t>
+          <t>STM32L151C6</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -59702,7 +59702,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32L151QD</t>
+          <t>STM32L151VB</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -59724,7 +59724,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32L152R8</t>
+          <t>STM32L152VB</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -59746,7 +59746,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32L151ZD</t>
+          <t>STM32L151V8</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -59768,7 +59768,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32L152ZD</t>
+          <t>STM32L152V8</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -59790,7 +59790,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32L152RD</t>
+          <t>STM32L151RB</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -59812,7 +59812,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32L151RD</t>
+          <t>STM32L152RB</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -59834,7 +59834,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32L152C6</t>
+          <t>STM32L151V8-A</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -59849,14 +59849,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32L152VD</t>
+          <t>STM32L151VB-A</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -59871,14 +59871,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32L152CB-A</t>
+          <t>STM32L151CB-A</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -59893,14 +59893,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32L151VD</t>
+          <t>STM32L151UC</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -59915,14 +59915,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32L152V8-A</t>
+          <t>STM32L151R8</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -59937,14 +59937,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32L152R6</t>
+          <t>STM32L152VE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -59966,7 +59966,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32L151C6</t>
+          <t>STM32L151VC-A</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -59981,14 +59981,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32L151VB</t>
+          <t>STM32L100C6-A</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -60003,14 +60003,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32L152VB</t>
+          <t>STM32L100C6</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -60025,14 +60025,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32L151V8</t>
+          <t>STM32L100RB-A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -60047,14 +60047,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32L152V8</t>
+          <t>STM32L100R8</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -60069,14 +60069,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32L151RB</t>
+          <t>STM32L100RB</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -60091,14 +60091,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32L152RB</t>
+          <t>STM32L100R8-A</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -60113,14 +60113,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
+          <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32L151V8-A</t>
+          <t>STM32L100RC</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -60134,380 +60134,6 @@
         </is>
       </c>
       <c r="D71" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>STM32L152VB-A</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>STM32L151VB-A</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>STM32L151RC-A</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>STM32L151CB-A</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>STM32L152RB-A</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>STM32L151UC</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Table 14. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>STM32L151R8</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>STM32L152VE</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>STM32L152RC-A</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STM32L151VC-A</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Table 13. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>STM32L100C6-A</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>STM32L100C6</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>STM32L100RB-A</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STM32L100R8</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32L100RB</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32L100R8-A</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Table 12. General operating conditions: V_DD min varies by condition (1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32L100RC</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
         <is>
           <t>Table 12. General operating conditions: V_DD min varies by condition (1.65 (1.65); 1.8 (1.8); 1.65 (1.65)) — the API's value stands</t>
         </is>

--- a/product_selector_out/STM32L1 series.xlsx
+++ b/product_selector_out/STM32L1 series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM98"/>
+  <dimension ref="A1:BN98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14.1171875" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162qd.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162qd.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162qc.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162qc.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162rc.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162qd.pdf</t>
         </is>
       </c>
@@ -3279,6 +3316,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162re.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162rc.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162qd.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162re.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162qc.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l162re.pdf</t>
         </is>
       </c>
@@ -5568,6 +5640,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -8184,6 +8296,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -9492,6 +9624,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -10146,6 +10288,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -10473,6 +10620,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -10800,6 +10952,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -11454,6 +11616,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -12435,6 +12612,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qc.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -15051,6 +15268,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -15705,6 +15932,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
@@ -16029,6 +16261,11 @@
       </c>
       <c r="BM57" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN57" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -16356,6 +16593,11 @@
       </c>
       <c r="BM58" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN58" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -16683,6 +16925,11 @@
       </c>
       <c r="BM59" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN59" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -17010,6 +17257,11 @@
       </c>
       <c r="BM60" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN60" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -17337,6 +17589,11 @@
       </c>
       <c r="BM61" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN61" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -17664,6 +17921,11 @@
       </c>
       <c r="BM62" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN62" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -17991,6 +18253,11 @@
       </c>
       <c r="BM63" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN63" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -18318,6 +18585,11 @@
       </c>
       <c r="BM64" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN64" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -18645,6 +18917,11 @@
       </c>
       <c r="BM65" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN65" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -18972,6 +19249,11 @@
       </c>
       <c r="BM66" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN66" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -19299,6 +19581,11 @@
       </c>
       <c r="BM67" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN67" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -19626,6 +19913,11 @@
       </c>
       <c r="BM68" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN68" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -19953,6 +20245,11 @@
       </c>
       <c r="BM69" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN69" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -20283,6 +20580,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN70" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -20607,6 +20909,11 @@
       </c>
       <c r="BM71" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN71" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qd.pdf</t>
         </is>
       </c>
@@ -20937,6 +21244,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN72" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -21261,6 +21573,11 @@
       </c>
       <c r="BM73" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN73" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -21588,6 +21905,11 @@
       </c>
       <c r="BM74" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN74" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -21915,6 +22237,11 @@
       </c>
       <c r="BM75" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN75" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -22242,6 +22569,11 @@
       </c>
       <c r="BM76" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN76" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -22569,6 +22901,11 @@
       </c>
       <c r="BM77" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN77" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -22896,6 +23233,11 @@
       </c>
       <c r="BM78" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN78" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -23223,6 +23565,11 @@
       </c>
       <c r="BM79" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN79" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -23550,6 +23897,11 @@
       </c>
       <c r="BM80" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN80" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -23877,6 +24229,11 @@
       </c>
       <c r="BM81" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN81" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
@@ -24207,6 +24564,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN82" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -24531,6 +24893,11 @@
       </c>
       <c r="BM83" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN83" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
@@ -24861,6 +25228,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN84" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -25185,6 +25557,11 @@
       </c>
       <c r="BM85" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN85" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -25515,6 +25892,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN86" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -25839,6 +26221,11 @@
       </c>
       <c r="BM87" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN87" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151cc.pdf</t>
         </is>
       </c>
@@ -26166,6 +26553,11 @@
       </c>
       <c r="BM88" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN88" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151c6.pdf</t>
         </is>
       </c>
@@ -26493,6 +26885,11 @@
       </c>
       <c r="BM89" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN89" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151qe.pdf</t>
         </is>
       </c>
@@ -26823,6 +27220,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BN90" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -27147,6 +27549,11 @@
       </c>
       <c r="BM91" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN91" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l151vd-x.pdf</t>
         </is>
       </c>
@@ -27474,6 +27881,11 @@
       </c>
       <c r="BM92" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN92" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
         </is>
       </c>
@@ -27801,6 +28213,11 @@
       </c>
       <c r="BM93" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN93" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
         </is>
       </c>
@@ -28128,6 +28545,11 @@
       </c>
       <c r="BM94" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN94" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
@@ -28455,6 +28877,11 @@
       </c>
       <c r="BM95" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN95" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
         </is>
       </c>
@@ -28782,6 +29209,11 @@
       </c>
       <c r="BM96" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN96" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100c6.pdf</t>
         </is>
       </c>
@@ -29109,6 +29541,11 @@
       </c>
       <c r="BM97" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN97" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
@@ -29436,12 +29873,17 @@
       </c>
       <c r="BM98" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN98" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l100rc.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -29462,16 +29904,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -29484,6 +29924,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -29503,7 +29944,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -29607,7 +30050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM98"/>
+  <dimension ref="A1:BN98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -29675,6 +30118,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30008,6 +30452,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -30103,6 +30552,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -30425,7 +30875,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30752,7 +31207,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31079,7 +31539,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31406,7 +31871,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31733,7 +32203,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32060,7 +32535,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -32392,6 +32872,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -32714,7 +33199,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33041,7 +33531,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33368,7 +33863,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -33695,7 +34195,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34022,7 +34527,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34349,7 +34859,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -34681,6 +35196,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -35003,7 +35523,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35330,7 +35855,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35657,7 +36187,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -35984,7 +36519,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36311,7 +36851,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36638,7 +37183,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -36965,7 +37515,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37297,6 +37852,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -37619,7 +38179,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -37946,7 +38511,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38273,7 +38843,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -38605,6 +39180,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -38927,7 +39507,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -39259,6 +39844,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -39586,6 +40176,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -39913,6 +40508,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -40235,7 +40835,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -40567,6 +41172,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -40889,7 +41499,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41216,7 +41831,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -41548,6 +42168,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -41870,7 +42495,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42197,7 +42827,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42524,7 +43159,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -42851,7 +43491,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43178,7 +43823,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43505,7 +44155,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -43832,7 +44487,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44164,6 +44824,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -44486,7 +45151,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -44818,6 +45488,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -45140,7 +45815,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM57" s="6" t="inlineStr">
+      <c r="BM57" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN57" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45467,7 +46147,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM58" s="6" t="inlineStr">
+      <c r="BM58" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN58" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -45794,7 +46479,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM59" s="6" t="inlineStr">
+      <c r="BM59" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN59" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46121,7 +46811,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM60" s="6" t="inlineStr">
+      <c r="BM60" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN60" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46448,7 +47143,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM61" s="6" t="inlineStr">
+      <c r="BM61" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN61" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -46775,7 +47475,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM62" s="6" t="inlineStr">
+      <c r="BM62" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN62" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47102,7 +47807,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM63" s="6" t="inlineStr">
+      <c r="BM63" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN63" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47429,7 +48139,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM64" s="6" t="inlineStr">
+      <c r="BM64" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN64" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -47756,7 +48471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM65" s="6" t="inlineStr">
+      <c r="BM65" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN65" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48083,7 +48803,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM66" s="6" t="inlineStr">
+      <c r="BM66" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN66" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48410,7 +49135,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM67" s="6" t="inlineStr">
+      <c r="BM67" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN67" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -48737,7 +49467,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM68" s="6" t="inlineStr">
+      <c r="BM68" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN68" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49064,7 +49799,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM69" s="6" t="inlineStr">
+      <c r="BM69" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN69" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -49396,6 +50136,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN70" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -49718,7 +50463,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM71" s="6" t="inlineStr">
+      <c r="BM71" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN71" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50050,6 +50800,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN72" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -50372,7 +51127,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM73" s="6" t="inlineStr">
+      <c r="BM73" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN73" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -50699,7 +51459,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM74" s="6" t="inlineStr">
+      <c r="BM74" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN74" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51026,7 +51791,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM75" s="6" t="inlineStr">
+      <c r="BM75" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN75" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51353,7 +52123,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM76" s="6" t="inlineStr">
+      <c r="BM76" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN76" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -51680,7 +52455,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM77" s="6" t="inlineStr">
+      <c r="BM77" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN77" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52007,7 +52787,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM78" s="6" t="inlineStr">
+      <c r="BM78" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN78" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52334,7 +53119,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM79" s="6" t="inlineStr">
+      <c r="BM79" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN79" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52661,7 +53451,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM80" s="6" t="inlineStr">
+      <c r="BM80" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN80" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -52988,7 +53783,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM81" s="6" t="inlineStr">
+      <c r="BM81" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN81" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53320,6 +54120,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN82" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
@@ -53642,7 +54447,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM83" s="6" t="inlineStr">
+      <c r="BM83" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN83" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -53974,6 +54784,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN84" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -54296,7 +55111,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM85" s="6" t="inlineStr">
+      <c r="BM85" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN85" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -54628,6 +55448,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN86" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
@@ -54950,7 +55775,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM87" s="6" t="inlineStr">
+      <c r="BM87" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN87" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55277,7 +56107,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM88" s="6" t="inlineStr">
+      <c r="BM88" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN88" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55604,7 +56439,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM89" s="6" t="inlineStr">
+      <c r="BM89" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN89" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -55936,6 +56776,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BN90" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
@@ -56258,7 +57103,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM91" s="6" t="inlineStr">
+      <c r="BM91" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN91" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56585,7 +57435,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM92" s="6" t="inlineStr">
+      <c r="BM92" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN92" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -56912,7 +57767,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM93" s="6" t="inlineStr">
+      <c r="BM93" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN93" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57239,7 +58099,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM94" s="6" t="inlineStr">
+      <c r="BM94" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN94" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57566,7 +58431,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM95" s="6" t="inlineStr">
+      <c r="BM95" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN95" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -57893,7 +58763,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM96" s="6" t="inlineStr">
+      <c r="BM96" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN96" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58220,7 +59095,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM97" s="6" t="inlineStr">
+      <c r="BM97" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN97" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58547,7 +59427,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM98" s="6" t="inlineStr">
+      <c r="BM98" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN98" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -58555,8 +59440,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
